--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>54.4941</v>
+        <v>51.2585</v>
       </c>
       <c r="E2" t="n">
-        <v>39.2478</v>
+        <v>34.9903</v>
       </c>
       <c r="F2" t="n">
-        <v>15.2459</v>
+        <v>16.2683</v>
       </c>
       <c r="G2" t="n">
-        <v>41.4354</v>
+        <v>32.5924</v>
       </c>
       <c r="H2" t="n">
-        <v>49.1673</v>
+        <v>17.4243</v>
       </c>
       <c r="I2" t="n">
-        <v>-7.731999999999999</v>
+        <v>15.1683</v>
       </c>
       <c r="J2" t="n">
-        <v>57.9084</v>
+        <v>54.9122</v>
       </c>
       <c r="K2" t="n">
-        <v>53.4491</v>
+        <v>23.8883</v>
       </c>
       <c r="L2" t="n">
-        <v>4.4598</v>
+        <v>31.024</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.4735</v>
+        <v>-22.32</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.2817</v>
+        <v>-6.4646</v>
       </c>
       <c r="O2" t="n">
-        <v>-12.1919</v>
+        <v>-15.8555</v>
       </c>
       <c r="P2" t="n">
-        <v>-18.0699</v>
+        <v>-10.4724</v>
       </c>
       <c r="Q2" t="n">
-        <v>-56.8797</v>
+        <v>-67.1469</v>
       </c>
       <c r="R2" t="n">
-        <v>38.8098</v>
+        <v>56.6743</v>
       </c>
       <c r="S2" t="n">
-        <v>35.5808</v>
+        <v>8.4177</v>
       </c>
       <c r="T2" t="n">
-        <v>28.6776</v>
+        <v>4.396</v>
       </c>
       <c r="U2" t="n">
-        <v>6.9034</v>
+        <v>4.0216</v>
       </c>
       <c r="V2" t="n">
-        <v>-4.4517</v>
+        <v>20.7207</v>
       </c>
       <c r="W2" t="n">
-        <v>9.541600000000001</v>
+        <v>42.8286</v>
       </c>
       <c r="X2" t="n">
-        <v>-13.9935</v>
+        <v>-22.1077</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>J. PUIDET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>50.6529</v>
+        <v>45.5655</v>
       </c>
       <c r="E3" t="n">
-        <v>30.9292</v>
+        <v>19.7204</v>
       </c>
       <c r="F3" t="n">
-        <v>19.7238</v>
+        <v>25.8453</v>
       </c>
       <c r="G3" t="n">
-        <v>8.2568</v>
+        <v>15.3795</v>
       </c>
       <c r="H3" t="n">
-        <v>44.4252</v>
+        <v>21.6157</v>
       </c>
       <c r="I3" t="n">
-        <v>-36.1687</v>
+        <v>-6.236200000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>36.4877</v>
+        <v>44.2574</v>
       </c>
       <c r="K3" t="n">
-        <v>51.72</v>
+        <v>28.7834</v>
       </c>
       <c r="L3" t="n">
-        <v>-15.2327</v>
+        <v>15.4742</v>
       </c>
       <c r="M3" t="n">
-        <v>-28.2308</v>
+        <v>-28.8777</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.2949</v>
+        <v>-7.167400000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-20.9356</v>
+        <v>-21.7104</v>
       </c>
       <c r="P3" t="n">
-        <v>1.848</v>
+        <v>4.5175</v>
       </c>
       <c r="Q3" t="n">
-        <v>-60.3707</v>
+        <v>-48.4605</v>
       </c>
       <c r="R3" t="n">
-        <v>62.2187</v>
+        <v>52.9782</v>
       </c>
       <c r="S3" t="n">
-        <v>26.7227</v>
+        <v>18.7913</v>
       </c>
       <c r="T3" t="n">
-        <v>16.7618</v>
+        <v>9.734500000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>9.960699999999999</v>
+        <v>9.0564</v>
       </c>
       <c r="V3" t="n">
-        <v>13.8252</v>
+        <v>6.8773</v>
       </c>
       <c r="W3" t="n">
-        <v>38.0503</v>
+        <v>14.1884</v>
       </c>
       <c r="X3" t="n">
-        <v>-24.225</v>
+        <v>-7.3113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. PUIDET</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D4" t="n">
-        <v>37.2968</v>
+        <v>45.0552</v>
       </c>
       <c r="E4" t="n">
-        <v>14.0096</v>
+        <v>32.5648</v>
       </c>
       <c r="F4" t="n">
-        <v>23.2876</v>
+        <v>12.4905</v>
       </c>
       <c r="G4" t="n">
-        <v>15.3795</v>
+        <v>32.8119</v>
       </c>
       <c r="H4" t="n">
-        <v>21.6157</v>
+        <v>12.9411</v>
       </c>
       <c r="I4" t="n">
-        <v>-6.236200000000001</v>
+        <v>19.8708</v>
       </c>
       <c r="J4" t="n">
-        <v>44.2574</v>
+        <v>45.1076</v>
       </c>
       <c r="K4" t="n">
-        <v>28.7834</v>
+        <v>16.2055</v>
       </c>
       <c r="L4" t="n">
-        <v>15.4742</v>
+        <v>28.9023</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.8777</v>
+        <v>-12.2957</v>
       </c>
       <c r="N4" t="n">
-        <v>-7.167400000000001</v>
+        <v>-3.2641</v>
       </c>
       <c r="O4" t="n">
-        <v>-21.7104</v>
+        <v>-9.0312</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5175</v>
+        <v>8.4191</v>
       </c>
       <c r="Q4" t="n">
-        <v>-48.4605</v>
+        <v>-29.9795</v>
       </c>
       <c r="R4" t="n">
-        <v>52.9782</v>
+        <v>38.399</v>
       </c>
       <c r="S4" t="n">
-        <v>10.5225</v>
+        <v>1.1043</v>
       </c>
       <c r="T4" t="n">
-        <v>4.0241</v>
+        <v>0.7599</v>
       </c>
       <c r="U4" t="n">
-        <v>6.4984</v>
+        <v>0.3445999999999999</v>
       </c>
       <c r="V4" t="n">
-        <v>6.8773</v>
+        <v>2.7197</v>
       </c>
       <c r="W4" t="n">
-        <v>14.1884</v>
+        <v>16.6773</v>
       </c>
       <c r="X4" t="n">
-        <v>-7.3113</v>
+        <v>-13.9574</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>24.2641</v>
+        <v>44.2345</v>
       </c>
       <c r="E5" t="n">
-        <v>15.1971</v>
+        <v>26.0637</v>
       </c>
       <c r="F5" t="n">
-        <v>9.067299999999999</v>
+        <v>18.1713</v>
       </c>
       <c r="G5" t="n">
-        <v>32.5924</v>
+        <v>8.2568</v>
       </c>
       <c r="H5" t="n">
-        <v>17.4243</v>
+        <v>44.4252</v>
       </c>
       <c r="I5" t="n">
-        <v>15.1683</v>
+        <v>-36.1687</v>
       </c>
       <c r="J5" t="n">
-        <v>54.9122</v>
+        <v>36.4877</v>
       </c>
       <c r="K5" t="n">
-        <v>23.8883</v>
+        <v>51.72</v>
       </c>
       <c r="L5" t="n">
-        <v>31.024</v>
+        <v>-15.2327</v>
       </c>
       <c r="M5" t="n">
-        <v>-22.32</v>
+        <v>-28.2308</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.4646</v>
+        <v>-7.2949</v>
       </c>
       <c r="O5" t="n">
-        <v>-15.8555</v>
+        <v>-20.9356</v>
       </c>
       <c r="P5" t="n">
-        <v>-10.4724</v>
+        <v>1.848</v>
       </c>
       <c r="Q5" t="n">
-        <v>-67.1469</v>
+        <v>-60.3707</v>
       </c>
       <c r="R5" t="n">
-        <v>56.6743</v>
+        <v>62.2187</v>
       </c>
       <c r="S5" t="n">
-        <v>-18.5765</v>
+        <v>20.3042</v>
       </c>
       <c r="T5" t="n">
-        <v>-15.3974</v>
+        <v>11.8961</v>
       </c>
       <c r="U5" t="n">
-        <v>-3.179</v>
+        <v>8.407999999999999</v>
       </c>
       <c r="V5" t="n">
-        <v>20.7207</v>
+        <v>13.8252</v>
       </c>
       <c r="W5" t="n">
-        <v>42.8286</v>
+        <v>38.0503</v>
       </c>
       <c r="X5" t="n">
-        <v>-22.1077</v>
+        <v>-24.225</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>19.4228</v>
+        <v>36.758</v>
       </c>
       <c r="E6" t="n">
-        <v>7.6997</v>
+        <v>22.7517</v>
       </c>
       <c r="F6" t="n">
-        <v>11.7228</v>
+        <v>14.0062</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.5715</v>
+        <v>41.4354</v>
       </c>
       <c r="H6" t="n">
-        <v>11.9116</v>
+        <v>49.1673</v>
       </c>
       <c r="I6" t="n">
-        <v>-16.4829</v>
+        <v>-7.731999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>9.2651</v>
+        <v>57.9084</v>
       </c>
       <c r="K6" t="n">
-        <v>15.4379</v>
+        <v>53.4491</v>
       </c>
       <c r="L6" t="n">
-        <v>-6.1724</v>
+        <v>4.4598</v>
       </c>
       <c r="M6" t="n">
-        <v>-13.8367</v>
+        <v>-16.4735</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.5261</v>
+        <v>-4.2817</v>
       </c>
       <c r="O6" t="n">
-        <v>-10.3104</v>
+        <v>-12.1919</v>
       </c>
       <c r="P6" t="n">
-        <v>16.6329</v>
+        <v>-18.0699</v>
       </c>
       <c r="Q6" t="n">
-        <v>-20.1236</v>
+        <v>-56.8797</v>
       </c>
       <c r="R6" t="n">
-        <v>36.7567</v>
+        <v>38.8098</v>
       </c>
       <c r="S6" t="n">
-        <v>8.2636</v>
+        <v>17.8448</v>
       </c>
       <c r="T6" t="n">
-        <v>8.667199999999999</v>
+        <v>12.1812</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4037999999999998</v>
+        <v>5.6634</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9023000000000002</v>
+        <v>-4.4517</v>
       </c>
       <c r="W6" t="n">
-        <v>9.890500000000001</v>
+        <v>9.541600000000001</v>
       </c>
       <c r="X6" t="n">
-        <v>-10.7931</v>
+        <v>-13.9935</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,70 +952,70 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>19.0084</v>
+        <v>20.4173</v>
       </c>
       <c r="E7" t="n">
-        <v>16.3589</v>
+        <v>6.2429</v>
       </c>
       <c r="F7" t="n">
-        <v>2.649699999999999</v>
+        <v>14.1743</v>
       </c>
       <c r="G7" t="n">
-        <v>32.8119</v>
+        <v>-4.5715</v>
       </c>
       <c r="H7" t="n">
-        <v>12.9411</v>
+        <v>11.9116</v>
       </c>
       <c r="I7" t="n">
-        <v>19.8708</v>
+        <v>-16.4829</v>
       </c>
       <c r="J7" t="n">
-        <v>45.1076</v>
+        <v>9.2651</v>
       </c>
       <c r="K7" t="n">
-        <v>16.2055</v>
+        <v>15.4379</v>
       </c>
       <c r="L7" t="n">
-        <v>28.9023</v>
+        <v>-6.1724</v>
       </c>
       <c r="M7" t="n">
-        <v>-12.2957</v>
+        <v>-13.8367</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.2641</v>
+        <v>-3.5261</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.0312</v>
+        <v>-10.3104</v>
       </c>
       <c r="P7" t="n">
-        <v>8.4191</v>
+        <v>16.6329</v>
       </c>
       <c r="Q7" t="n">
-        <v>-29.9795</v>
+        <v>-20.1236</v>
       </c>
       <c r="R7" t="n">
-        <v>38.399</v>
+        <v>36.7567</v>
       </c>
       <c r="S7" t="n">
-        <v>-24.9427</v>
+        <v>9.2582</v>
       </c>
       <c r="T7" t="n">
-        <v>-15.4462</v>
+        <v>7.2106</v>
       </c>
       <c r="U7" t="n">
-        <v>-9.496</v>
+        <v>2.0474</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7197</v>
+        <v>-0.9023000000000002</v>
       </c>
       <c r="W7" t="n">
-        <v>16.6773</v>
+        <v>9.890500000000001</v>
       </c>
       <c r="X7" t="n">
-        <v>-13.9574</v>
+        <v>-10.7931</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>22</v>
       </c>
       <c r="D8" t="n">
-        <v>17.0469</v>
+        <v>7.480300000000002</v>
       </c>
       <c r="E8" t="n">
-        <v>5.007299999999999</v>
+        <v>-5.723999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>12.0395</v>
+        <v>13.204</v>
       </c>
       <c r="G8" t="n">
         <v>-13.5669</v>
@@ -1078,13 +1078,13 @@
         <v>29.7747</v>
       </c>
       <c r="S8" t="n">
-        <v>21.4727</v>
+        <v>11.9061</v>
       </c>
       <c r="T8" t="n">
-        <v>19.3646</v>
+        <v>8.6334</v>
       </c>
       <c r="U8" t="n">
-        <v>2.1083</v>
+        <v>3.2728</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5367</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>4.4512</v>
+        <v>1.8591</v>
       </c>
       <c r="E9" t="n">
-        <v>9.291599999999999</v>
+        <v>-0.3255</v>
       </c>
       <c r="F9" t="n">
-        <v>-4.8405</v>
+        <v>2.1846</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9940000000000002</v>
+        <v>0.2568</v>
       </c>
       <c r="H9" t="n">
-        <v>6.9575</v>
+        <v>-2.5851</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.963200000000001</v>
+        <v>2.8419</v>
       </c>
       <c r="J9" t="n">
-        <v>8.8575</v>
+        <v>1.4072</v>
       </c>
       <c r="K9" t="n">
-        <v>6.516</v>
+        <v>-2.2891</v>
       </c>
       <c r="L9" t="n">
-        <v>2.3415</v>
+        <v>3.6963</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.8635</v>
+        <v>-1.1505</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4411999999999999</v>
+        <v>-0.296</v>
       </c>
       <c r="O9" t="n">
-        <v>-8.3047</v>
+        <v>-0.8544999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-3.9014</v>
+        <v>2.2588</v>
       </c>
       <c r="Q9" t="n">
-        <v>-24.8464</v>
+        <v>-1.2321</v>
       </c>
       <c r="R9" t="n">
-        <v>20.9451</v>
+        <v>3.4909</v>
       </c>
       <c r="S9" t="n">
-        <v>22.6173</v>
+        <v>-1.137</v>
       </c>
       <c r="T9" t="n">
-        <v>15.3898</v>
+        <v>-0.2831</v>
       </c>
       <c r="U9" t="n">
-        <v>7.2274</v>
+        <v>-0.8539</v>
       </c>
       <c r="V9" t="n">
-        <v>-15.2583</v>
+        <v>0.4804</v>
       </c>
       <c r="W9" t="n">
-        <v>9.890700000000001</v>
+        <v>-0.2177</v>
       </c>
       <c r="X9" t="n">
-        <v>-25.1493</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>R. ROTCENKOVS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.2465</v>
+        <v>-0.6795</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.837</v>
+        <v>-0.8166</v>
       </c>
       <c r="F10" t="n">
-        <v>2.0835</v>
+        <v>0.1371</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2568</v>
+        <v>-0.4557</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.5851</v>
+        <v>-0.6584</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8419</v>
+        <v>0.2027</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4072</v>
+        <v>-0.619</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.2891</v>
+        <v>-0.6584</v>
       </c>
       <c r="L10" t="n">
-        <v>3.6963</v>
+        <v>0.0395</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1505</v>
+        <v>0.1632</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.296</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8544999999999999</v>
+        <v>0.1632</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2588</v>
+        <v>0.2053</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4909</v>
+        <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.7495</v>
+        <v>-0.1889</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7945</v>
+        <v>-0.1976</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.9550000000000001</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4804</v>
+        <v>-0.2402</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.2177</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. ROTCENKOVS</t>
+          <t>J. ORTEGA MORA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.7684</v>
+        <v>-2.0494</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8166</v>
+        <v>0.2606999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0481</v>
+        <v>-2.3101</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4557</v>
+        <v>-0.02349999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6584</v>
+        <v>-0.5127</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2027</v>
+        <v>0.4893</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.619</v>
+        <v>0.005100000000000032</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6584</v>
+        <v>0.0974</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0395</v>
+        <v>-0.09230000000000005</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1632</v>
+        <v>-0.02839999999999993</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.61</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1632</v>
+        <v>0.5816</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2053</v>
+        <v>0.6159</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.2053</v>
+        <v>0.6159</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2778</v>
+        <v>-0.2847000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1976</v>
+        <v>0.2556</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.08019999999999999</v>
+        <v>-0.5405</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2402</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. ORTEGA MORA</t>
+          <t>A. BUTKO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5411</v>
+        <v>-3.12</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05309999999999999</v>
+        <v>-2.6222</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4879</v>
+        <v>-0.4976999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.02349999999999999</v>
+        <v>-2.2062</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5127</v>
+        <v>-0.9961</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4893</v>
+        <v>-1.2101</v>
       </c>
       <c r="J12" t="n">
-        <v>0.005100000000000032</v>
+        <v>-1.5186</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0974</v>
+        <v>-0.2817</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.09230000000000005</v>
+        <v>-1.2368</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.02839999999999993</v>
+        <v>-0.6875999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.61</v>
+        <v>-0.7143999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5816</v>
+        <v>0.02690000000000015</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6159</v>
+        <v>1.6426</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6159</v>
+        <v>3.696</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7763</v>
+        <v>-1.4867</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0582</v>
+        <v>-0.2289</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.7182000000000001</v>
+        <v>-1.258</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.3573</v>
+        <v>-1.0697</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.1786</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.3573</v>
+        <v>-2.2483</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BUTKO</t>
+          <t>L. SAVIKJEVIKJ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.6455</v>
+        <v>-3.3845</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.5637</v>
+        <v>-3.7846</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0818</v>
+        <v>0.4001</v>
       </c>
       <c r="G13" t="n">
-        <v>-2.2062</v>
+        <v>-3.2247</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.9961</v>
+        <v>0.4828000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.2101</v>
+        <v>-3.7075</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.5186</v>
+        <v>-0.1269</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.2817</v>
+        <v>0.3343</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.2368</v>
+        <v>-0.4611999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.6875999999999999</v>
+        <v>-3.0977</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.7143999999999999</v>
+        <v>0.1484000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>0.02690000000000015</v>
+        <v>-3.2461</v>
       </c>
       <c r="P13" t="n">
-        <v>1.6426</v>
+        <v>-0.6161</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.0534</v>
+        <v>-3.2854</v>
       </c>
       <c r="R13" t="n">
-        <v>3.696</v>
+        <v>2.6695</v>
       </c>
       <c r="S13" t="n">
-        <v>-3.0122</v>
+        <v>-0.8088</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1703</v>
+        <v>-0.3722</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.842</v>
+        <v>-0.4365</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0697</v>
+        <v>1.2649</v>
       </c>
       <c r="W13" t="n">
-        <v>1.1786</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.2483</v>
+        <v>1.2649</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>L. SAVIKJEVIKJ</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,70 +1498,70 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.4253</v>
+        <v>-7.1934</v>
       </c>
       <c r="E14" t="n">
-        <v>-4.9624</v>
+        <v>0.1717000000000004</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4629</v>
+        <v>-7.3656</v>
       </c>
       <c r="G14" t="n">
-        <v>-3.2247</v>
+        <v>0.9940000000000002</v>
       </c>
       <c r="H14" t="n">
-        <v>0.4828000000000001</v>
+        <v>6.9575</v>
       </c>
       <c r="I14" t="n">
-        <v>-3.7075</v>
+        <v>-5.963200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.1269</v>
+        <v>8.8575</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3343</v>
+        <v>6.516</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4611999999999999</v>
+        <v>2.3415</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0977</v>
+        <v>-7.8635</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1484000000000001</v>
+        <v>0.4411999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.2461</v>
+        <v>-8.3047</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6161</v>
+        <v>-3.9014</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.2854</v>
+        <v>-24.8464</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6695</v>
+        <v>20.9451</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.8496</v>
+        <v>10.9725</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.55</v>
+        <v>6.2701</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.2996</v>
+        <v>4.7025</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2649</v>
+        <v>-15.2583</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>9.890700000000001</v>
       </c>
       <c r="X14" t="n">
-        <v>1.2649</v>
+        <v>-25.1493</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>-12.9459</v>
+        <v>-11.7097</v>
       </c>
       <c r="E15" t="n">
-        <v>-9.489599999999999</v>
+        <v>-8.757400000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.456399999999999</v>
+        <v>-2.9524</v>
       </c>
       <c r="G15" t="n">
         <v>-1.9661</v>
@@ -1624,13 +1624,13 @@
         <v>1.2319</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.489</v>
+        <v>-0.2529</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7090000000000001</v>
+        <v>0.0232</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.7799</v>
+        <v>-0.276</v>
       </c>
       <c r="V15" t="n">
         <v>-3.5358</v>
@@ -1657,13 +1657,13 @@
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>-45.1429</v>
+        <v>-37.517</v>
       </c>
       <c r="E16" t="n">
-        <v>-46.7002</v>
+        <v>-40.5247</v>
       </c>
       <c r="F16" t="n">
-        <v>1.557399999999999</v>
+        <v>3.0078</v>
       </c>
       <c r="G16" t="n">
         <v>-17.8769</v>
@@ -1702,13 +1702,13 @@
         <v>34.4972</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4275999999999999</v>
+        <v>7.198599999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-2.7381</v>
+        <v>3.4375</v>
       </c>
       <c r="U16" t="n">
-        <v>2.3105</v>
+        <v>3.7611</v>
       </c>
       <c r="V16" t="n">
         <v>-3.6351</v>
@@ -1735,13 +1735,13 @@
         <v>26</v>
       </c>
       <c r="D17" t="n">
-        <v>156.4146</v>
+        <v>186.9749</v>
       </c>
       <c r="E17" t="n">
-        <v>71.3186</v>
+        <v>80.21119999999996</v>
       </c>
       <c r="F17" t="n">
-        <v>85.09610000000001</v>
+        <v>106.7637</v>
       </c>
       <c r="G17" t="n">
         <v>87.83530000000002</v>
@@ -1780,13 +1780,13 @@
         <v>382.9632000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>71.07840000000002</v>
+        <v>101.6387</v>
       </c>
       <c r="T17" t="n">
-        <v>54.82379999999999</v>
+        <v>63.7163</v>
       </c>
       <c r="U17" t="n">
-        <v>16.255</v>
+        <v>37.92159999999999</v>
       </c>
       <c r="V17" t="n">
         <v>12.90109999999999</v>
